--- a/data/trans_bre/IP19C07-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C07-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 15,29</t>
+          <t>-8,78; 15,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 17,35</t>
+          <t>-7,01; 17,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 10,6</t>
+          <t>-10,74; 11,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 12,06</t>
+          <t>-2,94; 13,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-45,4; 194,5</t>
+          <t>-49,3; 170,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-42,21; 206,13</t>
+          <t>-41,39; 227,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-76,41; 193,58</t>
+          <t>-76,02; 237,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-43,47; 289,88</t>
+          <t>-35,86; 290,69</t>
         </is>
       </c>
     </row>
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 14,04</t>
+          <t>-6,91; 13,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 10,29</t>
+          <t>-11,38; 10,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 16,39</t>
+          <t>2,35; 16,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 17,36</t>
+          <t>-2,39; 17,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-68,27; 859,35</t>
+          <t>-71,12; 849,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-67,59; 161,91</t>
+          <t>-68,44; 160,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-23,16; 363,35</t>
+          <t>-28,93; 371,6</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 20,18</t>
+          <t>-2,8; 21,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 17,85</t>
+          <t>-3,01; 18,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 18,91</t>
+          <t>-2,11; 18,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,49; 8,75</t>
+          <t>-16,57; 9,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-32,5; 424,23</t>
+          <t>-28,01; 495,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-45,71; 845,98</t>
+          <t>-42,31; 767,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 203,28</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 3,41</t>
+          <t>-12,18; 2,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 7,14</t>
+          <t>-3,7; 7,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 4,91</t>
+          <t>-5,99; 5,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 5,52</t>
+          <t>-4,98; 5,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,66; 42,44</t>
+          <t>-69,26; 28,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,14; 321,32</t>
+          <t>-54,17; 338,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-65,99; 155,54</t>
+          <t>-66,82; 177,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-68,09; 270,65</t>
+          <t>-70,37; 305,6</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 8,76</t>
+          <t>-5,9; 9,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,54; -2,22</t>
+          <t>-15,56; -1,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 12,88</t>
+          <t>-1,87; 12,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 9,49</t>
+          <t>-1,98; 9,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-62,58; 396,72</t>
+          <t>-70,89; 375,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-93,13; -14,58</t>
+          <t>-92,72; 2,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-33,65; 567,54</t>
+          <t>-35,53; 519,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-75,38; —</t>
         </is>
       </c>
     </row>
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,34; 26,94</t>
+          <t>2,4; 26,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-17,62; 15,26</t>
+          <t>-16,33; 16,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 13,23</t>
+          <t>-10,07; 13,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 9,19</t>
+          <t>-8,79; 6,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 1038,05</t>
+          <t>-8,31; 1081,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-67,73; 121,89</t>
+          <t>-62,14; 120,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-86,86; 533,34</t>
+          <t>-77,21; inf</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 6,77</t>
+          <t>-1,18; 6,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 3,1</t>
+          <t>-4,0; 3,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 5,91</t>
+          <t>-0,52; 5,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 5,18</t>
+          <t>-0,86; 5,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 84,59</t>
+          <t>-9,52; 84,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-36,93; 38,12</t>
+          <t>-33,25; 39,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 127,19</t>
+          <t>-8,25; 130,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 122,43</t>
+          <t>-12,85; 126,85</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C07-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C07-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 15,29</t>
+          <t>-7,44; 16,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 17,93</t>
+          <t>-7,38; 16,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 11,69</t>
+          <t>-11,3; 11,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 13,44</t>
+          <t>-3,58; 12,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-49,3; 170,57</t>
+          <t>-41,41; 239,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-41,39; 227,01</t>
+          <t>-42,24; 212,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-76,02; 237,43</t>
+          <t>-78,22; 235,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-35,86; 290,69</t>
+          <t>-40,79; 324,36</t>
         </is>
       </c>
     </row>
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 13,4</t>
+          <t>-6,06; 15,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 10,7</t>
+          <t>-11,74; 10,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,35; 16,38</t>
+          <t>2,51; 15,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 17,04</t>
+          <t>-1,92; 18,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-71,12; 849,49</t>
+          <t>-68,29; 736,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-68,44; 160,48</t>
+          <t>-66,69; 170,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,93; 371,6</t>
+          <t>-26,06; 397,41</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 21,28</t>
+          <t>-3,86; 20,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 18,89</t>
+          <t>-2,75; 18,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 18,86</t>
+          <t>-2,05; 20,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,57; 9,11</t>
+          <t>-17,29; 8,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-28,01; 495,07</t>
+          <t>-46,17; 439,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-42,31; 767,35</t>
+          <t>-38,97; 937,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 207,89</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 2,45</t>
+          <t>-12,43; 3,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 7,55</t>
+          <t>-2,94; 7,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 5,52</t>
+          <t>-6,09; 5,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 5,56</t>
+          <t>-4,73; 5,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-69,26; 28,41</t>
+          <t>-68,66; 37,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,17; 338,71</t>
+          <t>-53,5; 355,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-66,82; 177,24</t>
+          <t>-68,56; 151,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-70,37; 305,6</t>
+          <t>-74,39; 333,55</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 9,67</t>
+          <t>-5,09; 9,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,56; -1,12</t>
+          <t>-15,61; -1,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 12,62</t>
+          <t>-1,92; 13,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 9,44</t>
+          <t>-2,28; 8,61</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-70,89; 375,98</t>
+          <t>-61,45; 319,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-92,72; 2,65</t>
+          <t>-93,36; -8,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-35,53; 519,45</t>
+          <t>-36,53; 462,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-75,38; —</t>
+          <t>-82,1; 1093,92</t>
         </is>
       </c>
     </row>
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,4; 26,01</t>
+          <t>0,65; 26,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,33; 16,53</t>
+          <t>-16,94; 15,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 13,95</t>
+          <t>-12,79; 10,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 6,87</t>
+          <t>-8,77; 7,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 1081,98</t>
+          <t>-22,79; 990,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-62,14; 120,99</t>
+          <t>-67,56; 129,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-77,21; inf</t>
+          <t>-96,22; 305,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 6,79</t>
+          <t>-0,99; 6,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 3,27</t>
+          <t>-4,17; 3,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 5,79</t>
+          <t>-0,65; 6,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 5,54</t>
+          <t>-0,95; 5,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 84,68</t>
+          <t>-7,75; 88,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-33,25; 39,83</t>
+          <t>-33,57; 39,54</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 130,16</t>
+          <t>-11,12; 126,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,85; 126,85</t>
+          <t>-13,14; 121,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C07-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C07-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,68</t>
+          <t>3,87</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>48,83%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 16,73</t>
+          <t>-8,34; 15,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 16,89</t>
+          <t>-7,99; 17,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-11,3; 11,5</t>
+          <t>-10,66; 10,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 12,4</t>
+          <t>-3,65; 12,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-41,41; 239,95</t>
+          <t>-45,4; 194,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-42,24; 212,32</t>
+          <t>-42,21; 206,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-78,22; 235,49</t>
+          <t>-76,41; 193,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-40,79; 324,36</t>
+          <t>-43,68; 288,82</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,07</t>
+          <t>6,43</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>74,9%</t>
         </is>
       </c>
     </row>
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 15,0</t>
+          <t>-6,13; 14,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,74; 10,15</t>
+          <t>-11,2; 10,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 15,69</t>
+          <t>2,4; 16,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 18,34</t>
+          <t>-2,72; 16,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-68,29; 736,9</t>
+          <t>-68,27; 859,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-66,69; 170,91</t>
+          <t>-67,59; 161,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,06; 397,41</t>
+          <t>-27,19; 356,62</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,75</t>
+          <t>-4,59</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-31,98%</t>
+          <t>-37,0%</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 20,19</t>
+          <t>-2,96; 20,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 18,9</t>
+          <t>-2,8; 17,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 20,29</t>
+          <t>-2,93; 18,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,29; 8,71</t>
+          <t>-19,11; 7,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-46,17; 439,54</t>
+          <t>-32,5; 424,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-38,97; 937,86</t>
+          <t>-45,71; 845,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 207,89</t>
+          <t>-100,0; 181,85</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>0,75</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,43; 3,37</t>
+          <t>-12,25; 3,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 7,81</t>
+          <t>-3,15; 7,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 5,36</t>
+          <t>-6,01; 4,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 5,62</t>
+          <t>-4,77; 6,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-68,66; 37,97</t>
+          <t>-66,66; 42,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-53,5; 355,29</t>
+          <t>-52,14; 321,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-68,56; 151,02</t>
+          <t>-65,99; 155,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-74,39; 333,55</t>
+          <t>-64,5; 310,37</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,63</t>
+          <t>2,75</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>104,33%</t>
+          <t>103,56%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 9,95</t>
+          <t>-5,01; 8,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,61; -1,7</t>
+          <t>-16,54; -2,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 13,2</t>
+          <t>-2,36; 12,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 8,61</t>
+          <t>-2,16; 9,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-61,45; 319,77</t>
+          <t>-62,58; 396,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-93,36; -8,29</t>
+          <t>-93,13; -14,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-36,53; 462,95</t>
+          <t>-33,65; 567,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-82,1; 1093,92</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1,18</t>
+          <t>-1,06</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-27,96%</t>
+          <t>-24,53%</t>
         </is>
       </c>
     </row>
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,65; 26,07</t>
+          <t>1,34; 26,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,94; 15,73</t>
+          <t>-17,62; 15,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 10,54</t>
+          <t>-10,83; 13,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 7,04</t>
+          <t>-8,37; 10,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-22,79; 990,19</t>
+          <t>-8,55; 1038,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-67,56; 129,1</t>
+          <t>-67,73; 121,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-96,22; 305,08</t>
+          <t>-86,86; 533,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,14</t>
+          <t>2,04</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>33,97%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 6,77</t>
+          <t>-1,24; 6,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 3,29</t>
+          <t>-4,59; 3,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 6,02</t>
+          <t>-0,89; 5,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 5,45</t>
+          <t>-1,2; 5,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 88,31</t>
+          <t>-10,33; 84,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-33,57; 39,54</t>
+          <t>-36,93; 38,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 126,01</t>
+          <t>-12,96; 127,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-13,14; 121,48</t>
+          <t>-17,38; 115,08</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C07-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP19C07-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,195 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>3,42</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4,65</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,92</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,87</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>24,25%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>33,14%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-8,57%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>48,83%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>3.415072323003654</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>4.654885312163118</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.9151535348646572</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>3.865814116766512</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.2425307411670118</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.3314343715954995</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.0857352733795185</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.488278652875603</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-8,34; 15,29</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-7,99; 17,35</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-10,66; 10,6</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-3,65; 12,82</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-45,4; 194,5</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-42,21; 206,13</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-76,41; 193,58</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-43,68; 288,82</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-8.343707237508612</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-7.990939320292136</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-10.65834063814177</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-3.648186553211657</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.4539946635871617</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.4221251556449607</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.7641310265251463</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.4367736868550637</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>15.29346926566491</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>17.34829191565411</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>10.59825708808845</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>12.82035976087892</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.945035397200202</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>2.061330805343088</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>1.935760999363575</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>2.888180678999614</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>3,96</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,76</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>8,65</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,43</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>64,47%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-6,28%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>644,23%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>74,9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-6,13; 14,04</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-11,2; 10,29</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2,4; 16,39</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-2,72; 16,74</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-68,27; 859,35</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-67,59; 161,91</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-27,19; 356,62</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>3.960588923561106</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.7611358516754638</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>8.647647481248438</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>6.434500950825129</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.6447220327798526</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.06282360831322101</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>6.442270077744021</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.7490069761101484</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>7,93</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7,05</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6,7</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-4,59</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>92,74%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>108,27%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>188,49%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-37,0%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-6.132763239791132</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-11.19889876993643</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>2.399413955800812</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-2.72181930466357</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.6827449767058779</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.6759238152641919</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="n">
+        <v>-0.2719287983980413</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-2,96; 20,18</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-2,8; 17,85</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-2,93; 18,91</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-19,11; 7,81</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-32,5; 424,23</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-45,71; 845,98</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 181,85</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>14.04454214203982</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>10.29242368684466</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>16.39498815967212</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>16.74380871334188</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>8.593522864150883</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.619068821161542</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="n">
+        <v>3.566233787683867</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +815,195 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-4,77</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,83</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,47</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,75</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-33,71%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>39,33%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-7,56%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16,82%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>7.930087379122885</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>7.050513551201998</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>6.700889767981774</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-4.593041049209639</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.9274253831152625</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1.08273802279196</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>1.884867612166687</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.3699760787710907</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-12,25; 3,41</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-3,15; 7,14</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-6,01; 4,91</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-4,77; 6,07</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-66,66; 42,44</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-52,14; 321,32</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-65,99; 155,54</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-64,5; 310,37</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-2.955892189123064</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.80375506750399</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-2.92936495963139</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-19.11366104054219</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.3249897213678438</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.4570916168485084</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>20.17960424490049</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>17.85100350395432</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>18.91381053029719</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>7.805214038972871</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>4.242302640916467</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>8.459826328883258</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="n">
+        <v>1.818502195933663</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>1,7</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-7,99</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4,7</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,75</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>28,88%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-71,16%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>81,07%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>103,56%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-5,01; 8,76</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-16,54; -2,22</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,36; 12,88</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-2,16; 9,91</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-62,58; 396,72</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-93,13; -14,58</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-33,65; 567,54</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-4.768427762491183</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1.827366578929347</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.472769984636158</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.7527087176596802</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.3371098469582418</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.3932830699094542</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.0756067986416364</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.1682410297106605</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>13,23</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-1,6</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0,42</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-1,06</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>180,26%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-7,74%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4,81%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-24,53%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-12.25015019859785</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-3.151147032796069</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-6.011623401678859</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-4.768237802282126</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.6666422949797505</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.5213922756662287</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.6598695944294216</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.6450287672027015</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>1,34; 26,94</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-17,62; 15,26</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-10,83; 13,23</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-8,37; 10,0</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-8,55; 1038,05</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-67,73; 121,89</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-86,86; 533,34</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3.414408383806328</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>7.137412265085269</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>4.905484252723589</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>6.073746209095827</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.4244425860248866</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>3.213216464080323</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1.555420851321293</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>3.103719675621817</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1011,289 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>2,71</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,32</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2,65</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,04</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>27,1%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-3,14%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>44,15%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>33,97%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>1.696862585327417</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-7.990268771199076</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>4.702488268428566</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>2.75020764369343</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.2887706509469637</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.7115861512895187</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.8106909777877441</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>1.035576785422379</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-1,24; 6,77</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-4,59; 3,1</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-0,89; 5,91</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-1,2; 5,27</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-10,33; 84,59</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-36,93; 38,12</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-12,96; 127,19</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-17,38; 115,08</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-5.013617418522206</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-16.53916233422879</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-2.355001376670903</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.163398858071381</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.6257553675249712</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.931257216163338</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.3364833472735003</v>
+      </c>
+      <c r="J17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>8.758354251657462</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>-2.224464307747291</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>12.87883375136467</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>9.91271979946522</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>3.967205199901563</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>-0.1458407322513939</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>5.675426053690915</v>
+      </c>
+      <c r="J18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>13.22716342761941</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-1.600228103604553</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0.4175927461207332</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-1.057146178396082</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>1.802639293663623</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.07736510591394587</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>0.04807971211905721</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>-0.245305498739178</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>1.336213494892913</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-17.61650300697063</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-10.82670744221914</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-8.368977717732605</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.08548300758829397</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.6773463275562526</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-0.868592301782622</v>
+      </c>
+      <c r="J20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>26.94263003023693</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>15.26341519338198</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>13.22942767785787</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>10.00242256825433</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>10.38046877513034</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1.218880691308069</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>5.333444552614042</v>
+      </c>
+      <c r="J21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>2.706734963927339</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.3239713681567266</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>2.647279491371634</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>2.039890918303843</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>0.2710043057010303</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.03142818795182173</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>0.4414991128565835</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.3397124292848328</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-1.242519053760315</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-4.590804751353579</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.8850515542765068</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-1.202423021376001</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.1033334687691289</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.3693288146193122</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.1295668947867956</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.1737802033011122</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>6.774260780757604</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>3.101453157285637</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>5.912382155220659</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>5.271109402559059</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.8458785503806862</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.3812244385868487</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>1.271942254766788</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>1.150806671649125</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1301,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
